--- a/data/trans_camb/IP2004-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 3,91</t>
+          <t>-5,51; 3,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,79</t>
+          <t>-6,97; 1,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; -0,29</t>
+          <t>-7,87; -0,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,65</t>
+          <t>0,92; 6,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 2,23</t>
+          <t>-2,64; 2,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,57</t>
+          <t>-3,16; 1,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,64</t>
+          <t>-2,66; 1,83</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 280,33</t>
+          <t>-100,0; 293,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-88,15; 368,88</t>
+          <t>-84,66; 342,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-83,63; 269,06</t>
+          <t>-79,2; 285,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 2,43</t>
+          <t>-6,79; 2,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 2,65</t>
+          <t>-7,23; 2,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; -0,83</t>
+          <t>-8,89; -1,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,39</t>
+          <t>-2,47; 1,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,0</t>
+          <t>-3,75; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 5,04</t>
+          <t>-1,58; 4,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,46</t>
+          <t>-3,68; 1,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 0,76</t>
+          <t>-4,0; 0,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,61</t>
+          <t>-4,14; 0,63</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 294,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 389,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 193,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 146,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,62; 6,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,5</t>
+          <t>0,0; 7,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 6,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 3,66</t>
+          <t>-3,48; 4,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -0,68</t>
+          <t>-5,63; -0,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,23</t>
+          <t>-4,26; 1,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,28</t>
+          <t>-1,35; 3,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,52</t>
+          <t>-2,1; 1,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,41</t>
+          <t>-2,08; 2,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 2,73</t>
+          <t>-2,15; 2,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 4,97</t>
+          <t>-0,33; 5,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,9</t>
+          <t>-3,08; 0,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,88</t>
+          <t>-4,61; 0,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 0,53</t>
+          <t>-4,87; 0,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 0,64</t>
+          <t>-4,64; 0,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,21</t>
+          <t>-2,5; 1,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,0</t>
+          <t>-2,04; 2,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 0,28</t>
+          <t>-3,32; 0,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-71,13; 328,78</t>
+          <t>-77,38; 245,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-35,02; 544,76</t>
+          <t>-19,8; 654,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 157,13</t>
+          <t>-100,0; 186,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-83,15; 58,54</t>
+          <t>-81,83; 52,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,28; 39,15</t>
+          <t>-86,92; 71,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,42; 37,79</t>
+          <t>-83,34; 80,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,48; 72,45</t>
+          <t>-64,37; 61,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,02; 110,05</t>
+          <t>-51,71; 101,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,3; 26,2</t>
+          <t>-82,44; 12,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 4,96</t>
+          <t>-3,47; 5,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 2,93</t>
+          <t>-5,19; 2,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 1,66</t>
+          <t>-5,93; 1,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 4,2</t>
+          <t>-4,95; 4,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 2,47</t>
+          <t>-5,97; 2,22</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,84</t>
+          <t>-7,13; 1,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 3,63</t>
+          <t>-2,97; 3,58</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,59</t>
+          <t>-4,43; 1,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,36</t>
+          <t>-5,36; 0,2</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,76; 309,45</t>
+          <t>-61,79; 298,91</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-80,43; 234,05</t>
+          <t>-82,05; 161,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,54; 120,48</t>
+          <t>-88,79; 184,38</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-65,27; 123,03</t>
+          <t>-64,86; 136,04</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,43; 84,13</t>
+          <t>-75,08; 78,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 42,14</t>
+          <t>-87,25; 60,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,26; 112,8</t>
+          <t>-45,23; 116,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-64,3; 50,16</t>
+          <t>-66,68; 44,9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 16,64</t>
+          <t>-79,71; 15,11</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 5,88</t>
+          <t>-4,98; 6,48</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 1,43</t>
+          <t>-6,64; 1,67</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 4,17</t>
+          <t>-5,05; 4,85</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,91</t>
+          <t>-6,0; 0,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,19</t>
+          <t>-5,0; 2,16</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 7,36</t>
+          <t>-3,42; 7,42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 2,11</t>
+          <t>-3,68; 2,09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,79</t>
+          <t>-4,43; 0,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 3,84</t>
+          <t>-3,2; 3,6</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 596,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 200,56</t>
+          <t>-100,0; 254,9</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 164,24</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-81,65; 442,95</t>
+          <t>-89,11; 307,65</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,66</t>
+          <t>-1,52; 1,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,53</t>
+          <t>-1,71; 1,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,09; -0,44</t>
+          <t>-3,05; -0,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,78</t>
+          <t>-2,05; 0,79</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 0,08</t>
+          <t>-2,62; 0,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,75</t>
+          <t>-2,01; 0,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,81</t>
+          <t>-1,37; 0,71</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,3</t>
+          <t>-1,69; 0,33</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; -0,15</t>
+          <t>-2,1; -0,13</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 82,23</t>
+          <t>-44,4; 79,4</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 77,75</t>
+          <t>-47,8; 75,95</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-83,75; -15,19</t>
+          <t>-81,28; -14,37</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-56,88; 42,16</t>
+          <t>-58,35; 42,9</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 6,93</t>
+          <t>-70,93; 5,6</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-61,53; 34,87</t>
+          <t>-55,95; 48,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-38,73; 35,69</t>
+          <t>-41,26; 30,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-48,41; 13,31</t>
+          <t>-49,48; 15,32</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-62,0; -7,28</t>
+          <t>-61,5; -3,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 3,69</t>
+          <t>-5,55; 3,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 1,43</t>
+          <t>-7,14; 1,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -0,25</t>
+          <t>-8,47; -0,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,05</t>
+          <t>0,8; 5,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,3</t>
+          <t>-2,63; 2,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,41</t>
+          <t>-3,15; 1,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,83</t>
+          <t>-2,66; 1,56</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 293,03</t>
+          <t>-100,0; 277,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,66; 342,98</t>
+          <t>-84,03; 336,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-79,2; 285,09</t>
+          <t>-81,55; 264,67</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 2,44</t>
+          <t>-6,56; 2,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 2,15</t>
+          <t>-7,12; 2,61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -1,06</t>
+          <t>-9,56; -1,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -913,27 +913,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,0</t>
+          <t>-4,05; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,23</t>
+          <t>-1,59; 4,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 1,24</t>
+          <t>-4,08; 1,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,96</t>
+          <t>-4,07; 0,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,63</t>
+          <t>-4,43; 0,59</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 380,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 389,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,0; 265,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 146,71</t>
+          <t>-100,0; 220,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,67</t>
+          <t>0,62; 7,53</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,42</t>
+          <t>0,0; 7,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,91</t>
+          <t>0,0; 7,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,03</t>
+          <t>-3,46; 3,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; -0,68</t>
+          <t>-5,64; -0,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 1,64</t>
+          <t>-4,19; 1,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 3,64</t>
+          <t>-1,61; 3,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,57</t>
+          <t>-2,12; 1,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 2,68</t>
+          <t>-2,02; 2,53</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,42</t>
+          <t>-1,81; 2,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 5,13</t>
+          <t>-0,65; 4,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 0,81</t>
+          <t>-3,23; 0,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 0,99</t>
+          <t>-4,84; 1,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,83</t>
+          <t>-5,14; 0,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,98</t>
+          <t>-4,78; 0,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,15</t>
+          <t>-2,6; 1,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 2,03</t>
+          <t>-2,13; 2,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 0,08</t>
+          <t>-3,39; 0,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-77,38; 245,43</t>
+          <t>-68,36; 342,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-19,8; 654,87</t>
+          <t>-34,69; 536,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 186,16</t>
+          <t>-100,0; 174,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-81,83; 52,53</t>
+          <t>-81,07; 56,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,92; 71,03</t>
+          <t>-88,6; 32,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-83,34; 80,58</t>
+          <t>-87,49; 53,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,37; 61,39</t>
+          <t>-63,75; 60,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,71; 101,5</t>
+          <t>-54,06; 106,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-82,44; 12,64</t>
+          <t>-81,65; 15,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 5,24</t>
+          <t>-3,42; 4,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 2,56</t>
+          <t>-5,27; 2,8</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 1,97</t>
+          <t>-5,63; 1,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 4,36</t>
+          <t>-5,36; 4,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 2,22</t>
+          <t>-5,88; 2,7</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1,07</t>
+          <t>-7,38; 1,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,58</t>
+          <t>-3,35; 3,15</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 1,36</t>
+          <t>-4,6; 1,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 0,2</t>
+          <t>-5,55; 0,08</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,79; 298,91</t>
+          <t>-59,3; 251,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,05; 161,42</t>
+          <t>-82,59; 187,83</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-88,79; 184,38</t>
+          <t>-90,38; 187,46</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-64,86; 136,04</t>
+          <t>-70,09; 133,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,08; 78,39</t>
+          <t>-72,73; 97,06</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,25; 60,44</t>
+          <t>-89,89; 52,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-45,23; 116,15</t>
+          <t>-49,09; 88,78</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 44,9</t>
+          <t>-64,95; 52,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-79,71; 15,11</t>
+          <t>-79,17; 13,82</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 6,48</t>
+          <t>-4,68; 5,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 1,67</t>
+          <t>-6,91; 1,33</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 4,85</t>
+          <t>-5,33; 4,27</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,91</t>
+          <t>-5,11; 1,57</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,16</t>
+          <t>-4,96; 2,22</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 7,42</t>
+          <t>-2,99; 7,48</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,09</t>
+          <t>-4,0; 2,26</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,78</t>
+          <t>-4,39; 0,72</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,6</t>
+          <t>-2,96; 4,04</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 254,9</t>
+          <t>-100,0; 267,17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 164,24</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-89,11; 307,65</t>
+          <t>-83,88; 452,55</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,66</t>
+          <t>-1,48; 1,84</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,49</t>
+          <t>-1,55; 1,55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -0,43</t>
+          <t>-2,96; -0,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,79</t>
+          <t>-1,97; 0,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,05</t>
+          <t>-2,52; 0,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 0,91</t>
+          <t>-2,0; 0,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,71</t>
+          <t>-1,32; 0,83</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,33</t>
+          <t>-1,67; 0,35</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,1; -0,13</t>
+          <t>-2,08; -0,1</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 79,4</t>
+          <t>-44,72; 90,05</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 75,95</t>
+          <t>-42,74; 79,58</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-81,28; -14,37</t>
+          <t>-81,13; -10,31</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-58,35; 42,9</t>
+          <t>-56,19; 41,6</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-70,93; 5,6</t>
+          <t>-71,54; 8,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-55,95; 48,45</t>
+          <t>-57,59; 40,84</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-41,26; 30,35</t>
+          <t>-39,24; 35,86</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-49,48; 15,32</t>
+          <t>-50,41; 15,36</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-61,5; -3,79</t>
+          <t>-61,68; -3,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2004-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP2004-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,79</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,38</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,51</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,27</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,45</t>
+          <t>-3,18</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,33</t>
+          <t>-0,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 3,3</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 1,29</t>
+          <t>0,0; 3,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,47; -0,35</t>
+          <t>0,88; 5,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,8</t>
+          <t>-5,5; 3,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>-6,42; 1,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,34</t>
+          <t>-7,19; -0,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,24</t>
+          <t>-2,73; 2,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,36</t>
+          <t>-3,07; 1,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,56</t>
+          <t>-2,88; 1,62</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-29,43%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-63,84%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-82,97%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>-80,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-16,38%</t>
+          <t>-18,32%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 277,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 280,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-84,03; 336,66</t>
+          <t>-88,15; 368,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 264,67</t>
+          <t>-84,92; 285,42</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,11</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,8</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,86</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,54</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-1,57</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-3,89</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,11</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,94</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>-0,85</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,55</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 2,72</t>
+          <t>-2,41; 1,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 2,61</t>
+          <t>-4,0; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,56; -1,07</t>
+          <t>-1,3; 5,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 1,38</t>
+          <t>-6,41; 2,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,0</t>
+          <t>-6,99; 2,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,49</t>
+          <t>-9,85; -0,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 1,44</t>
+          <t>-4,02; 1,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 0,9</t>
+          <t>-4,27; 0,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,59</t>
+          <t>-4,5; 0,48</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-13,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>108,47%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-39,51%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-40,36%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-13,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>118,18%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>-36,27%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-63,27%</t>
+          <t>-65,96%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 380,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 294,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-91,0; 265,0</t>
+          <t>-90,45; 193,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 220,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,29</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>2,38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,22</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,1</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,23</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>-0,08</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,53</t>
+          <t>-3,37; 3,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>-5,66; -0,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,89</t>
+          <t>-4,25; 1,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 3,47</t>
+          <t>0,0; 5,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,64; -0,68</t>
+          <t>0,0; 7,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 1,42</t>
+          <t>0,0; 8,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 3,33</t>
+          <t>-1,62; 3,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,95</t>
+          <t>-2,41; 1,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 2,53</t>
+          <t>-2,08; 2,4</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-10,45%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-61,59%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-10,45%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-58,57%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>67,62%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,1%</t>
+          <t>-6,45%</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,76</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,08</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,79</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,93</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,76</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,08</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,51</t>
+          <t>-1,24</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,81</t>
+          <t>-5,06; 0,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 4,73</t>
+          <t>-5,25; 0,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,69</t>
+          <t>-4,71; 1,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,01</t>
+          <t>-2,03; 2,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 0,35</t>
+          <t>-0,88; 4,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 0,86</t>
+          <t>-2,92; 1,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,08</t>
+          <t>-2,49; 1,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 2,07</t>
+          <t>-2,06; 2,0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,05</t>
+          <t>-3,09; 0,66</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-44,65%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-52,76%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-45,51%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>97,73%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-52,13%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-44,65%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-52,76%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-50,88%</t>
+          <t>-38,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-51,15%</t>
+          <t>-42,14%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,36; 342,77</t>
+          <t>-83,15; 58,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 536,7</t>
+          <t>-88,28; 39,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 174,72</t>
+          <t>-87,2; 50,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-81,07; 56,03</t>
+          <t>-71,13; 328,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-88,6; 32,94</t>
+          <t>-35,02; 544,76</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-87,49; 53,39</t>
+          <t>-100,0; 242,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-63,75; 60,18</t>
+          <t>-64,48; 72,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 106,83</t>
+          <t>-53,02; 110,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-81,65; 15,95</t>
+          <t>-78,19; 51,63</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,41</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,66</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-2,99</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-0,85</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,7</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,1</t>
+          <t>-1,62</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>-2,37</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 4,58</t>
+          <t>-5,22; 4,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 2,8</t>
+          <t>-5,94; 2,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 1,98</t>
+          <t>-7,62; 0,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 4,5</t>
+          <t>-3,54; 4,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 2,7</t>
+          <t>-4,89; 2,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 1,02</t>
+          <t>-5,72; 1,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,15</t>
+          <t>-2,93; 3,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 1,44</t>
+          <t>-4,08; 1,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 0,08</t>
+          <t>-5,27; 0,55</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-7,17%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-28,71%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-51,74%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>19,7%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-21,77%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-43,71%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-7,17%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-28,71%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-53,61%</t>
+          <t>-41,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-49,79%</t>
+          <t>-48,11%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-59,3; 251,09</t>
+          <t>-65,27; 123,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,59; 187,83</t>
+          <t>-74,43; 84,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-90,38; 187,46</t>
+          <t>-85,66; 48,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-70,09; 133,34</t>
+          <t>-60,76; 309,45</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-72,73; 97,06</t>
+          <t>-80,43; 234,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-89,89; 52,27</t>
+          <t>-90,87; 131,94</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 88,78</t>
+          <t>-47,26; 112,8</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-64,95; 52,51</t>
+          <t>-64,3; 50,16</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-79,17; 13,82</t>
+          <t>-80,16; 20,21</t>
         </is>
       </c>
     </row>
@@ -1704,39 +1704,39 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,13</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,95</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0,28</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-0,38</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-2,29</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,13</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-1,11</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>-0,95</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,1</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-0,95</t>
-        </is>
-      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>-1,65</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>-0,44</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 5,7</t>
+          <t>-5,09; 0,91</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 1,33</t>
+          <t>-4,99; 2,19</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 4,27</t>
+          <t>-3,99; 4,84</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 1,57</t>
+          <t>-4,95; 5,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 2,22</t>
+          <t>-6,01; 1,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 7,48</t>
+          <t>-5,47; 4,16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 2,26</t>
+          <t>-3,67; 2,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,72</t>
+          <t>-4,3; 0,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 4,04</t>
+          <t>-3,22; 3,2</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-56,03%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-47,19%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-11,12%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-67,74%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-30,49%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-56,03%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-47,19%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>-32,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>-16,22%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 596,13</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 267,17</t>
+          <t>-100,0; 200,56</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-83,88; 452,55</t>
+          <t>-84,93; 400,72</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-0,68</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-0,06</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,6</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-1,08</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,84</t>
+          <t>-2,03; 0,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,55</t>
+          <t>-2,6; 0,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,96; -0,38</t>
+          <t>-2,18; 0,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 0,83</t>
+          <t>-1,47; 1,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,06</t>
+          <t>-1,55; 1,53</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,79</t>
+          <t>-3,02; -0,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,83</t>
+          <t>-1,29; 0,81</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,35</t>
+          <t>-1,62; 0,3</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,08; -0,1</t>
+          <t>-2,03; -0,13</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-20,95%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-43,66%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-23,98%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>4,18%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-2,17%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-58,06%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-20,95%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-43,66%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-23,18%</t>
+          <t>-53,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-39,41%</t>
+          <t>-38,08%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,72; 90,05</t>
+          <t>-56,88; 42,16</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-42,74; 79,58</t>
+          <t>-72,14; 6,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-81,13; -10,31</t>
+          <t>-61,35; 35,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-56,19; 41,6</t>
+          <t>-41,07; 82,23</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-71,54; 8,42</t>
+          <t>-45,11; 77,75</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 40,84</t>
+          <t>-82,35; -8,63</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 35,86</t>
+          <t>-38,73; 35,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-50,41; 15,36</t>
+          <t>-48,41; 13,31</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-61,68; -3,18</t>
+          <t>-60,86; -5,64</t>
         </is>
       </c>
     </row>
